--- a/Firmware/Modules/FlashLock/FlashLock_Validation.xlsx
+++ b/Firmware/Modules/FlashLock/FlashLock_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
